--- a/per-stock/FIX/financials.xlsx
+++ b/per-stock/FIX/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70149275648</v>
+        <v>69221294080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>72758657024</v>
+        <v>71836778496</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57.47736</v>
+        <v>56.8123</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.03916</v>
+        <v>36.812992</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.921018</v>
+        <v>6.8294625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1099853568</v>
+        <v>1382966000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>35202424</v>
+        <v>35183967</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1992.74</v>
+        <v>1967.41</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D44</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C44</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B44</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B43:E43)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B41:E41)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D39</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C39</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B39</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B38:E38)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1668,13 +2148,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1683,7 +2163,6 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1717,11 +2196,6 @@
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1744,7 +2218,6 @@
       <c r="F2" s="3" t="n">
         <v>-595572</v>
       </c>
-      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1767,7 +2240,6 @@
       <c r="F3" s="3" t="n">
         <v>0.186</v>
       </c>
-      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1790,7 +2262,6 @@
       <c r="F4" s="3" t="n">
         <v>246958000</v>
       </c>
-      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1813,7 +2284,6 @@
       <c r="F5" s="3" t="n">
         <v>-3202000</v>
       </c>
-      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1836,7 +2306,6 @@
       <c r="F6" s="3" t="n">
         <v>-3202000</v>
       </c>
-      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1859,7 +2328,6 @@
       <c r="F7" s="3" t="n">
         <v>169289000</v>
       </c>
-      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1882,7 +2350,6 @@
       <c r="F8" s="3" t="n">
         <v>34125000</v>
       </c>
-      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1905,7 +2372,6 @@
       <c r="F9" s="3" t="n">
         <v>1427870000</v>
       </c>
-      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1928,7 +2394,6 @@
       <c r="F10" s="3" t="n">
         <v>243756000</v>
       </c>
-      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1951,7 +2416,6 @@
       <c r="F11" s="3" t="n">
         <v>209631000</v>
       </c>
-      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1974,7 +2438,6 @@
       <c r="F12" s="3" t="n">
         <v>2648000</v>
       </c>
-      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1997,7 +2460,6 @@
       <c r="F13" s="3" t="n">
         <v>1619000</v>
       </c>
-      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2020,7 +2482,6 @@
       <c r="F14" s="3" t="n">
         <v>4267000</v>
       </c>
-      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2043,7 +2504,6 @@
       <c r="F15" s="3" t="n">
         <v>171895428</v>
       </c>
-      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2066,7 +2526,6 @@
       <c r="F16" s="3" t="n">
         <v>169289000</v>
       </c>
-      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2089,7 +2548,6 @@
       <c r="F17" s="3" t="n">
         <v>1622744000</v>
       </c>
-      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2112,7 +2570,6 @@
       <c r="F18" s="3" t="n">
         <v>209098000</v>
       </c>
-      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2123,7 +2580,9 @@
       <c r="B19" s="3" t="n">
         <v>35251000</v>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="n">
+        <v>35318000</v>
+      </c>
       <c r="D19" s="3" t="n">
         <v>35365000</v>
       </c>
@@ -2133,9 +2592,6 @@
       <c r="F19" s="3" t="n">
         <v>35605000</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>35692000</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2146,7 +2602,9 @@
       <c r="B20" s="3" t="n">
         <v>35207000</v>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="n">
+        <v>35260000</v>
+      </c>
       <c r="D20" s="3" t="n">
         <v>35307000</v>
       </c>
@@ -2156,9 +2614,6 @@
       <c r="F20" s="3" t="n">
         <v>35524000</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>35601000</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2169,7 +2624,9 @@
       <c r="B21" s="3" t="n">
         <v>10.51</v>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="n">
+        <v>9.369999999999999</v>
+      </c>
       <c r="D21" s="3" t="n">
         <v>8.25</v>
       </c>
@@ -2179,9 +2636,6 @@
       <c r="F21" s="3" t="n">
         <v>4.75</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>4.09</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2192,7 +2646,9 @@
       <c r="B22" s="3" t="n">
         <v>10.52</v>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="n">
+        <v>9.380000000000001</v>
+      </c>
       <c r="D22" s="3" t="n">
         <v>8.26</v>
       </c>
@@ -2202,9 +2658,6 @@
       <c r="F22" s="3" t="n">
         <v>4.77</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>4.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2227,7 +2680,6 @@
       <c r="F23" s="3" t="n">
         <v>169289000</v>
       </c>
-      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2250,7 +2702,6 @@
       <c r="F24" s="3" t="n">
         <v>169289000</v>
       </c>
-      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2273,7 +2724,6 @@
       <c r="F25" s="3" t="n">
         <v>169289000</v>
       </c>
-      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2296,7 +2746,6 @@
       <c r="F26" s="3" t="n">
         <v>169289000</v>
       </c>
-      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2319,7 +2768,6 @@
       <c r="F27" s="3" t="n">
         <v>169289000</v>
       </c>
-      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2342,7 +2790,6 @@
       <c r="F28" s="3" t="n">
         <v>38723000</v>
       </c>
-      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2365,7 +2812,6 @@
       <c r="F29" s="3" t="n">
         <v>208012000</v>
       </c>
-      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2388,7 +2834,6 @@
       <c r="F30" s="3" t="n">
         <v>-3178000</v>
       </c>
-      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2411,7 +2856,6 @@
       <c r="F31" s="3" t="n">
         <v>24000</v>
       </c>
-      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2434,7 +2878,6 @@
       <c r="F32" s="3" t="n">
         <v>-3202000</v>
       </c>
-      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2457,7 +2900,6 @@
       <c r="F33" s="3" t="n">
         <v>556000</v>
       </c>
-      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2480,7 +2922,6 @@
       <c r="F34" s="3" t="n">
         <v>3758000</v>
       </c>
-      <c r="G34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2503,7 +2944,6 @@
       <c r="F35" s="3" t="n">
         <v>2648000</v>
       </c>
-      <c r="G35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2526,7 +2966,6 @@
       <c r="F36" s="3" t="n">
         <v>1619000</v>
       </c>
-      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2549,7 +2988,6 @@
       <c r="F37" s="3" t="n">
         <v>4267000</v>
       </c>
-      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2572,7 +3010,6 @@
       <c r="F38" s="3" t="n">
         <v>208542000</v>
       </c>
-      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2595,7 +3032,6 @@
       <c r="F39" s="3" t="n">
         <v>194874000</v>
       </c>
-      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2618,7 +3054,6 @@
       <c r="F40" s="3" t="n">
         <v>194874000</v>
       </c>
-      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2641,7 +3076,6 @@
       <c r="F41" s="3" t="n">
         <v>403416000</v>
       </c>
-      <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2664,7 +3098,6 @@
       <c r="F42" s="3" t="n">
         <v>1427870000</v>
       </c>
-      <c r="G42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2687,7 +3120,6 @@
       <c r="F43" s="3" t="n">
         <v>1831286000</v>
       </c>
-      <c r="G43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2710,14 +3142,13 @@
       <c r="F44" s="3" t="n">
         <v>1831286000</v>
       </c>
-      <c r="G44" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4179,7 +4610,1577 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>5936242</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>5946145</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>5851415</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>5841913</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>5815389</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>35187123</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>35177220</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>35271950</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>35281452</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>35307976</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>41123365</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>41123365</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>41123365</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>41123365</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>41123365</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>339084000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>483358000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>394054000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>283650000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>278206000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1324759000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>938091000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>873297000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>591983000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>429668000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2854127000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2594000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2369384000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2044229000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1844855000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>870138000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>716703000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>671305000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>343680000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>186255000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1324759000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>938091000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>873297000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>591983000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>429668000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>300005000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>338132000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>258056000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>210630000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>210364000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2815048000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>2448774000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2233386000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1971209000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1777013000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2854102000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2587837000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2364708000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2032540000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1840789000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2815048000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2448774000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2233386000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1971209000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1777013000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2815048000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2448774000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2233386000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1971209000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1777013000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>500449000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>496006000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>401121000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>388298000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>367508000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2926810000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2581055000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>2271408000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1997434000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1782457000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>388276000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>363314000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>362688000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>361662000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>361653000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>411000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>411000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>411000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>411000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>411000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>411000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>411000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>411000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>411000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>411000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>4123298000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>3992395000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3544465000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>3092520000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2792205000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>492505000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>598545000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>512242000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>392921000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>380961000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>149554000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>153000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>120639000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>118735000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>104596000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>3892000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>3892000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>3892000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>3892000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>339059000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>441653000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>389378000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>271961000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>274140000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>300005000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>302590000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>258056000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>210630000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>210364000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>39054000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>139063000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>131322000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>61331000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>63776000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>3630793000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>3393850000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3032223000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>2699599000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>2411244000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>249784000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>125234000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>229756000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>268721000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>351779000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2345279000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2120262000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1734272000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1546306000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1267373000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>2345279000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>2120262000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1734272000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1546306000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1267373000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>41705000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>4676000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>11689000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>4066000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n">
+        <v>35542000</v>
+      </c>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
+        <v>28158000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>6163000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>4676000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>11689000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>4066000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n">
+        <v>6163000</v>
+      </c>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n">
+        <v>6042000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>278182000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>291722000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>356397000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>264495000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>191950000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>757523000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>814927000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>707122000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>608388000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>596076000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>37933000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>109786000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>41990000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>35121000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>35413000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>719590000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>705141000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>665132000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>573267000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>560663000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
+        <v>8793000</v>
+      </c>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>5568000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>719590000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>696348000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>665132000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>573267000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>560663000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>6938346000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>6441169000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>5777851000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>5063729000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>4569218000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>2437415000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>2330616000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>2074323000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2020450000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1971719000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>26495000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>24920000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>24181000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>19201000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>19247000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>83183000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>84139000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>77904000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>84344000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>83409000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>83183000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>84139000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>77904000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>84344000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>83409000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>1490289000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1510683000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1360089000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1379226000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1347345000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>464774000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>485168000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>431921000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>451446000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>441502000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1025515000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1025515000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>928168000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>927780000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>905843000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>837448000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>710874000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>612149000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>537679000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>521718000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n">
+        <v>-292627000</v>
+      </c>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>-249637000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>837448000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1003501000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>612149000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>537679000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>521718000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n">
+        <v>48024000</v>
+      </c>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>26233000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>837448000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>322922000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>612149000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>537679000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>521718000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n">
+        <v>435627000</v>
+      </c>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>359034000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n">
+        <v>173616000</v>
+      </c>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n">
+        <v>128652000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>23312000</v>
+      </c>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n">
+        <v>12898000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>4500931000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>4110553000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>3703528000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>3043279000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>2597499000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>177588000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>138560000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>63160000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>37991000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>50859000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>93947000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>84066000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>78830000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>70732000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>63045000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>3179232000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>2906029000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>2701015000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>2602846000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>2278837000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>373962000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>328171000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>394720000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>440501000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>541861000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>2805270000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>2577858000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>2306295000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>2162345000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>1736976000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>-19991000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>-19708000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>-18645000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-17028000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>-15632000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>2825261000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>2597566000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>2324940000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>2179373000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1752608000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>1050164000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>981898000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>860523000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>331710000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>204758000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>1050164000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>981898000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>860523000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>331710000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>204758000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5423,7 +7424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6736,7 +8737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
